--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_BOSCO MÉRIDA PATRIMONIO DE LA HUMANIDAD.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_BOSCO MÉRIDA PATRIMONIO DE LA HUMANIDAD.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>71.8293</v>
+        <v>88.9562</v>
       </c>
       <c r="E2" t="n">
-        <v>66.0338</v>
+        <v>77.99799999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>5.7955</v>
+        <v>10.9583</v>
       </c>
       <c r="G2" t="n">
         <v>32.2698</v>
@@ -610,13 +610,13 @@
         <v>62.2564</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.9626</v>
+        <v>14.1641</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.08</v>
+        <v>10.8845</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.8826</v>
+        <v>3.2801</v>
       </c>
       <c r="V2" t="n">
         <v>54.7509</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. GEDEAO YIMBU</t>
+          <t>J. RIBEIROS CARREIRAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>54.3572</v>
+        <v>43.0919</v>
       </c>
       <c r="E3" t="n">
-        <v>38.1529</v>
+        <v>38.5717</v>
       </c>
       <c r="F3" t="n">
-        <v>16.2037</v>
+        <v>4.520499999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>16.5182</v>
+        <v>39.6007</v>
       </c>
       <c r="H3" t="n">
-        <v>15.5751</v>
+        <v>-1.4136</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9428999999999998</v>
+        <v>41.014</v>
       </c>
       <c r="J3" t="n">
-        <v>31.8272</v>
+        <v>71.4757</v>
       </c>
       <c r="K3" t="n">
-        <v>25.5435</v>
+        <v>20.03</v>
       </c>
       <c r="L3" t="n">
-        <v>6.2835</v>
+        <v>51.4455</v>
       </c>
       <c r="M3" t="n">
-        <v>-15.3089</v>
+        <v>-31.8749</v>
       </c>
       <c r="N3" t="n">
-        <v>-9.968300000000001</v>
+        <v>-21.4435</v>
       </c>
       <c r="O3" t="n">
-        <v>-5.340599999999999</v>
+        <v>-10.4314</v>
       </c>
       <c r="P3" t="n">
-        <v>-21.864</v>
+        <v>5.5584</v>
       </c>
       <c r="Q3" t="n">
-        <v>-62.9976</v>
+        <v>-52.2507</v>
       </c>
       <c r="R3" t="n">
-        <v>41.134</v>
+        <v>57.8096</v>
       </c>
       <c r="S3" t="n">
-        <v>72.6122</v>
+        <v>1.7712</v>
       </c>
       <c r="T3" t="n">
-        <v>51.7145</v>
+        <v>3.6175</v>
       </c>
       <c r="U3" t="n">
-        <v>20.8978</v>
+        <v>-1.8461</v>
       </c>
       <c r="V3" t="n">
-        <v>-12.9096</v>
+        <v>-3.838699999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>17.6093</v>
+        <v>15.7296</v>
       </c>
       <c r="X3" t="n">
-        <v>-30.5186</v>
+        <v>-19.5682</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. PINILLA NUÑEZ</t>
+          <t>R. CARRETERO GONZALEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>22.9815</v>
+        <v>25.6214</v>
       </c>
       <c r="E4" t="n">
-        <v>22.9815</v>
+        <v>24.9972</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.6246000000000003</v>
       </c>
       <c r="G4" t="n">
-        <v>22.9815</v>
+        <v>6.142700000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>8.0517</v>
+        <v>6.1755</v>
       </c>
       <c r="I4" t="n">
-        <v>14.93</v>
+        <v>-0.03339999999999987</v>
       </c>
       <c r="J4" t="n">
-        <v>22.9815</v>
+        <v>20.652</v>
       </c>
       <c r="K4" t="n">
-        <v>8.0517</v>
+        <v>19.606</v>
       </c>
       <c r="L4" t="n">
-        <v>14.93</v>
+        <v>1.046</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-14.5094</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-13.43</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-1.0795</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>10.3759</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-26.6812</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>37.0573</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.4977</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>7.7408</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-4.2434</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>5.6056</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>23.2859</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-17.68</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MIAVIVULULU NZIKULU</t>
+          <t>J. PINILLA NUÑEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D5" t="n">
-        <v>22.5594</v>
+        <v>22.9815</v>
       </c>
       <c r="E5" t="n">
-        <v>11.1764</v>
+        <v>22.9815</v>
       </c>
       <c r="F5" t="n">
-        <v>11.383</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>20.8389</v>
+        <v>22.9815</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8941</v>
+        <v>8.0517</v>
       </c>
       <c r="I5" t="n">
-        <v>18.9447</v>
+        <v>14.93</v>
       </c>
       <c r="J5" t="n">
-        <v>28.4833</v>
+        <v>22.9815</v>
       </c>
       <c r="K5" t="n">
-        <v>10.0789</v>
+        <v>8.0517</v>
       </c>
       <c r="L5" t="n">
-        <v>18.4043</v>
+        <v>14.93</v>
       </c>
       <c r="M5" t="n">
-        <v>-7.6444</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-8.1844</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5403</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-9.6351</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-33.3516</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>23.7167</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>6.1286</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>8.808199999999999</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-2.68</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>5.2271</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>7.236499999999999</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.0094</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. CARRETERO GONZALEZ</t>
+          <t>J. MIAVIVULULU NZIKULU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>17.5706</v>
+        <v>21.1221</v>
       </c>
       <c r="E6" t="n">
-        <v>23.3613</v>
+        <v>8.5463</v>
       </c>
       <c r="F6" t="n">
-        <v>-5.790699999999999</v>
+        <v>12.5754</v>
       </c>
       <c r="G6" t="n">
-        <v>6.142700000000001</v>
+        <v>20.8389</v>
       </c>
       <c r="H6" t="n">
-        <v>6.1755</v>
+        <v>1.8941</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03339999999999987</v>
+        <v>18.9447</v>
       </c>
       <c r="J6" t="n">
-        <v>20.652</v>
+        <v>28.4833</v>
       </c>
       <c r="K6" t="n">
-        <v>19.606</v>
+        <v>10.0789</v>
       </c>
       <c r="L6" t="n">
-        <v>1.046</v>
+        <v>18.4043</v>
       </c>
       <c r="M6" t="n">
-        <v>-14.5094</v>
+        <v>-7.6444</v>
       </c>
       <c r="N6" t="n">
-        <v>-13.43</v>
+        <v>-8.1844</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0795</v>
+        <v>0.5403</v>
       </c>
       <c r="P6" t="n">
-        <v>10.3759</v>
+        <v>-9.6351</v>
       </c>
       <c r="Q6" t="n">
-        <v>-26.6812</v>
+        <v>-33.3516</v>
       </c>
       <c r="R6" t="n">
-        <v>37.0573</v>
+        <v>23.7167</v>
       </c>
       <c r="S6" t="n">
-        <v>-4.5535</v>
+        <v>4.6909</v>
       </c>
       <c r="T6" t="n">
-        <v>6.104800000000001</v>
+        <v>6.1785</v>
       </c>
       <c r="U6" t="n">
-        <v>-10.6585</v>
+        <v>-1.4875</v>
       </c>
       <c r="V6" t="n">
-        <v>5.6056</v>
+        <v>5.2271</v>
       </c>
       <c r="W6" t="n">
-        <v>23.2859</v>
+        <v>7.236499999999999</v>
       </c>
       <c r="X6" t="n">
-        <v>-17.68</v>
+        <v>-2.0094</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. ANDRADE</t>
+          <t>M. GEDEAO YIMBU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D7" t="n">
-        <v>15.8004</v>
+        <v>16.8106</v>
       </c>
       <c r="E7" t="n">
-        <v>9.540799999999997</v>
+        <v>10.7933</v>
       </c>
       <c r="F7" t="n">
-        <v>6.2595</v>
+        <v>6.0174</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.5336</v>
+        <v>16.5182</v>
       </c>
       <c r="H7" t="n">
-        <v>-7.5813</v>
+        <v>15.5751</v>
       </c>
       <c r="I7" t="n">
-        <v>5.047700000000001</v>
+        <v>0.9428999999999998</v>
       </c>
       <c r="J7" t="n">
-        <v>17.4062</v>
+        <v>31.8272</v>
       </c>
       <c r="K7" t="n">
-        <v>2.500899999999999</v>
+        <v>25.5435</v>
       </c>
       <c r="L7" t="n">
-        <v>14.9057</v>
+        <v>6.2835</v>
       </c>
       <c r="M7" t="n">
-        <v>-19.9403</v>
+        <v>-15.3089</v>
       </c>
       <c r="N7" t="n">
-        <v>-10.082</v>
+        <v>-9.968300000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-9.8583</v>
+        <v>-5.340599999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>1.6674</v>
+        <v>-21.864</v>
       </c>
       <c r="Q7" t="n">
-        <v>-28.3488</v>
+        <v>-62.9976</v>
       </c>
       <c r="R7" t="n">
-        <v>30.0165</v>
+        <v>41.134</v>
       </c>
       <c r="S7" t="n">
-        <v>8.480499999999999</v>
+        <v>35.066</v>
       </c>
       <c r="T7" t="n">
-        <v>5.6945</v>
+        <v>24.3546</v>
       </c>
       <c r="U7" t="n">
-        <v>2.7859</v>
+        <v>10.7111</v>
       </c>
       <c r="V7" t="n">
-        <v>8.1859</v>
+        <v>-12.9096</v>
       </c>
       <c r="W7" t="n">
-        <v>14.7886</v>
+        <v>17.6093</v>
       </c>
       <c r="X7" t="n">
-        <v>-6.6026</v>
+        <v>-30.5186</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. RIBEIROS CARREIRAS</t>
+          <t>E. ANDRADE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D8" t="n">
-        <v>11.3217</v>
+        <v>16.7953</v>
       </c>
       <c r="E8" t="n">
-        <v>14.1155</v>
+        <v>9.0106</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.793900000000002</v>
+        <v>7.7847</v>
       </c>
       <c r="G8" t="n">
-        <v>39.6007</v>
+        <v>-2.5336</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4136</v>
+        <v>-7.5813</v>
       </c>
       <c r="I8" t="n">
-        <v>41.014</v>
+        <v>5.047700000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>71.4757</v>
+        <v>17.4062</v>
       </c>
       <c r="K8" t="n">
-        <v>20.03</v>
+        <v>2.500899999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>51.4455</v>
+        <v>14.9057</v>
       </c>
       <c r="M8" t="n">
-        <v>-31.8749</v>
+        <v>-19.9403</v>
       </c>
       <c r="N8" t="n">
-        <v>-21.4435</v>
+        <v>-10.082</v>
       </c>
       <c r="O8" t="n">
-        <v>-10.4314</v>
+        <v>-9.8583</v>
       </c>
       <c r="P8" t="n">
-        <v>5.5584</v>
+        <v>1.6674</v>
       </c>
       <c r="Q8" t="n">
-        <v>-52.2507</v>
+        <v>-28.3488</v>
       </c>
       <c r="R8" t="n">
-        <v>57.8096</v>
+        <v>30.0165</v>
       </c>
       <c r="S8" t="n">
-        <v>-29.9987</v>
+        <v>9.4755</v>
       </c>
       <c r="T8" t="n">
-        <v>-20.8388</v>
+        <v>5.1643</v>
       </c>
       <c r="U8" t="n">
-        <v>-9.160400000000001</v>
+        <v>4.311</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.838699999999999</v>
+        <v>8.1859</v>
       </c>
       <c r="W8" t="n">
-        <v>15.7296</v>
+        <v>14.7886</v>
       </c>
       <c r="X8" t="n">
-        <v>-19.5682</v>
+        <v>-6.6026</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>7.6672</v>
+        <v>6.819600000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4172</v>
+        <v>-4.831</v>
       </c>
       <c r="F9" t="n">
-        <v>10.0844</v>
+        <v>11.6508</v>
       </c>
       <c r="G9" t="n">
         <v>-8.827500000000001</v>
@@ -1156,13 +1156,13 @@
         <v>18.8994</v>
       </c>
       <c r="S9" t="n">
-        <v>5.24</v>
+        <v>4.391999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>8.156599999999999</v>
+        <v>5.7431</v>
       </c>
       <c r="U9" t="n">
-        <v>-2.9168</v>
+        <v>-1.3506</v>
       </c>
       <c r="V9" t="n">
         <v>4.0288</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. GARRIDO SOTO</t>
+          <t>D. LEMOINE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>4.2969</v>
+        <v>3.608</v>
       </c>
       <c r="E10" t="n">
-        <v>8.324200000000001</v>
+        <v>0.1234000000000002</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.027299999999999</v>
+        <v>3.4847</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8221</v>
+        <v>4.787700000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3527</v>
+        <v>0.7788000000000002</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4692</v>
+        <v>4.0087</v>
       </c>
       <c r="J10" t="n">
-        <v>14.809</v>
+        <v>4.5203</v>
       </c>
       <c r="K10" t="n">
-        <v>9.1891</v>
+        <v>0.7120000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>5.6201</v>
+        <v>3.8085</v>
       </c>
       <c r="M10" t="n">
-        <v>-12.9872</v>
+        <v>0.2674</v>
       </c>
       <c r="N10" t="n">
-        <v>-7.8365</v>
+        <v>0.067</v>
       </c>
       <c r="O10" t="n">
-        <v>-5.150599999999999</v>
+        <v>0.2004</v>
       </c>
       <c r="P10" t="n">
-        <v>16.3054</v>
+        <v>1.6676</v>
       </c>
       <c r="Q10" t="n">
-        <v>-15.1934</v>
+        <v>-6.6703</v>
       </c>
       <c r="R10" t="n">
-        <v>31.4988</v>
+        <v>8.337999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>9.5822</v>
+        <v>0.1092</v>
       </c>
       <c r="T10" t="n">
-        <v>9.6601</v>
+        <v>1.0146</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0779</v>
+        <v>-0.9052</v>
       </c>
       <c r="V10" t="n">
-        <v>-23.4129</v>
+        <v>-2.9562</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.9514999999999999</v>
+        <v>1.2589</v>
       </c>
       <c r="X10" t="n">
-        <v>-22.4611</v>
+        <v>-4.215100000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. ÁLVAREZ GONZÁLEZ</t>
+          <t>N. RAMIREZ PRIETO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.8883</v>
+        <v>2.3206</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8883</v>
+        <v>0.3775000000000002</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1.9432</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8883</v>
+        <v>1.4037</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6442</v>
+        <v>1.5309</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2441</v>
+        <v>-0.1273</v>
       </c>
       <c r="J11" t="n">
-        <v>1.8883</v>
+        <v>1.1762</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6442</v>
+        <v>1.5802</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2441</v>
+        <v>-0.4041</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>0.2274999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>-0.04919999999999997</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.2766999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0.3705000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-3.1499</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.7794</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>0.784</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>0.7778</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>0.006099999999999967</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.5036</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.5733</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.0697</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. RAMIREZ PRIETO</t>
+          <t>C. ÁLVAREZ GONZÁLEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2184</v>
+        <v>1.8883</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6019</v>
+        <v>1.8883</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8201</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1.4037</v>
+        <v>1.8883</v>
       </c>
       <c r="H12" t="n">
-        <v>1.5309</v>
+        <v>0.6442</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1273</v>
+        <v>1.2441</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1762</v>
+        <v>1.8883</v>
       </c>
       <c r="K12" t="n">
-        <v>1.5802</v>
+        <v>0.6442</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.4041</v>
+        <v>1.2441</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2274999999999999</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.04919999999999997</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2766999999999999</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3705000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.1499</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.7794</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3184000000000001</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2014</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1169000000000001</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.5036</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5733</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0697</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. LEMOINE</t>
+          <t>A. REYES ALVAREZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.0994</v>
+        <v>0.8566</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.3139</v>
+        <v>0.2597</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4131</v>
+        <v>0.5969</v>
       </c>
       <c r="G13" t="n">
-        <v>4.787700000000001</v>
+        <v>0.2611</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7788000000000002</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>4.0087</v>
+        <v>0.2611</v>
       </c>
       <c r="J13" t="n">
-        <v>4.5203</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7120000000000001</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>3.8085</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2674</v>
+        <v>0.2611</v>
       </c>
       <c r="N13" t="n">
-        <v>0.067</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2004</v>
+        <v>0.2611</v>
       </c>
       <c r="P13" t="n">
-        <v>1.6676</v>
+        <v>0.1853</v>
       </c>
       <c r="Q13" t="n">
-        <v>-6.6703</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>8.337999999999999</v>
+        <v>0.1853</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.3995</v>
+        <v>0.0958</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4226</v>
+        <v>-0.0547</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.9769</v>
+        <v>0.1505</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.9562</v>
+        <v>0.3144</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2589</v>
+        <v>0.3144</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.215100000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. REYES ALVAREZ</t>
+          <t>F. GARRIDO SOTO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9305</v>
+        <v>0.2106000000000003</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2597</v>
+        <v>4.2568</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6708</v>
+        <v>-4.046500000000002</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2611</v>
+        <v>1.8221</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1.3527</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2611</v>
+        <v>0.4692</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>14.809</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>9.1891</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>5.6201</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2611</v>
+        <v>-12.9872</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>-7.8365</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2611</v>
+        <v>-5.150599999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1853</v>
+        <v>16.3054</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-15.1934</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1853</v>
+        <v>31.4988</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1696</v>
+        <v>5.4959</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0547</v>
+        <v>5.5935</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2243</v>
+        <v>-0.09710000000000002</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3144</v>
+        <v>-23.4129</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3144</v>
+        <v>-0.9514999999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-22.4611</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4047000000000005</v>
+        <v>-0.7915999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>8.203199999999999</v>
+        <v>5.3199</v>
       </c>
       <c r="F15" t="n">
-        <v>-7.7984</v>
+        <v>-6.111400000000001</v>
       </c>
       <c r="G15" t="n">
         <v>-3.5738</v>
@@ -1624,13 +1624,13 @@
         <v>11.673</v>
       </c>
       <c r="S15" t="n">
-        <v>7.1136</v>
+        <v>5.9174</v>
       </c>
       <c r="T15" t="n">
-        <v>9.4474</v>
+        <v>6.5642</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.3338</v>
+        <v>-0.6467999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>-2.5793</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0596</v>
+        <v>-1.9219</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5576</v>
+        <v>-1.0092</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6172</v>
+        <v>-0.9127</v>
       </c>
       <c r="G16" t="n">
         <v>-1.2418</v>
@@ -1702,13 +1702,13 @@
         <v>2.2234</v>
       </c>
       <c r="S16" t="n">
-        <v>1.774</v>
+        <v>-0.0883</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5171</v>
+        <v>-0.0497</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2569</v>
+        <v>-0.0386</v>
       </c>
       <c r="V16" t="n">
         <v>-1.8888</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.9712</v>
+        <v>-1.9465</v>
       </c>
       <c r="E17" t="n">
         <v>-1.6887</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2824</v>
+        <v>-0.2578</v>
       </c>
       <c r="G17" t="n">
         <v>-0.9517</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.093</v>
+        <v>-0.0684</v>
       </c>
       <c r="T17" t="n">
         <v>-0.1094</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0164</v>
+        <v>0.041</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. ALVAREZ GONZALEZ</t>
+          <t>J. MALPICA PEREZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.3042</v>
+        <v>-1.9979</v>
       </c>
       <c r="E18" t="n">
-        <v>-6.4808</v>
+        <v>-3.5401</v>
       </c>
       <c r="F18" t="n">
-        <v>3.1767</v>
+        <v>1.5422</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.7066</v>
+        <v>-1.2189</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5467</v>
+        <v>-0.03290000000000015</v>
       </c>
       <c r="I18" t="n">
-        <v>-4.2534</v>
+        <v>-1.1857</v>
       </c>
       <c r="J18" t="n">
-        <v>-4.1108</v>
+        <v>-2.4844</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9876</v>
+        <v>-0.03900000000000015</v>
       </c>
       <c r="L18" t="n">
-        <v>-5.0986</v>
+        <v>-2.4457</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4041999999999999</v>
+        <v>1.2657</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4409</v>
+        <v>0.005999999999999978</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8449</v>
+        <v>1.2597</v>
       </c>
       <c r="P18" t="n">
-        <v>2.0383</v>
+        <v>1.2971</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.1117</v>
       </c>
       <c r="R18" t="n">
-        <v>3.149999999999999</v>
+        <v>2.4088</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0063</v>
+        <v>0.7562</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.2583</v>
+        <v>0.05609999999999993</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2521</v>
+        <v>0.7</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6294</v>
+        <v>-2.8322</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6294</v>
+        <v>-2.8322</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MALPICA PEREZ</t>
+          <t>C. ALVAREZ GONZALEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.8476</v>
+        <v>-2.2993</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.3235</v>
+        <v>-5.6976</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4762000000000002</v>
+        <v>3.3982</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.2189</v>
+        <v>-3.7066</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.03290000000000015</v>
+        <v>0.5467</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1857</v>
+        <v>-4.2534</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.4844</v>
+        <v>-4.1108</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.03900000000000015</v>
+        <v>0.9876</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.4457</v>
+        <v>-5.0986</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2657</v>
+        <v>0.4041999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>0.005999999999999978</v>
+        <v>-0.4409</v>
       </c>
       <c r="O19" t="n">
-        <v>1.2597</v>
+        <v>0.8449</v>
       </c>
       <c r="P19" t="n">
-        <v>1.2971</v>
+        <v>2.0383</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.1117</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4088</v>
+        <v>3.149999999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0935</v>
+        <v>-0.001199999999999979</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7274999999999999</v>
+        <v>-0.4751</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3663</v>
+        <v>0.4738</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.8322</v>
+        <v>-0.6294</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.8322</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. GALLEGO CONTRERAS</t>
+          <t>D. VIGARIO CONSTANTINO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,76 +1966,76 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.1588</v>
+        <v>-6.3004</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.0169</v>
+        <v>-5.7424</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.141900000000001</v>
+        <v>-0.5581</v>
       </c>
       <c r="G20" t="n">
-        <v>-15.0776</v>
+        <v>-0.6682</v>
       </c>
       <c r="H20" t="n">
-        <v>-14.455</v>
+        <v>0.1856</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6222999999999994</v>
+        <v>-0.8541000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.971900000000001</v>
+        <v>-0.3813999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>-5.188099999999999</v>
+        <v>1.4942</v>
       </c>
       <c r="L20" t="n">
-        <v>3.2157</v>
+        <v>-1.8757</v>
       </c>
       <c r="M20" t="n">
-        <v>-13.1056</v>
+        <v>-0.2871</v>
       </c>
       <c r="N20" t="n">
-        <v>-9.266999999999999</v>
+        <v>-1.3086</v>
       </c>
       <c r="O20" t="n">
-        <v>-3.8385</v>
+        <v>1.0214</v>
       </c>
       <c r="P20" t="n">
-        <v>8.1524</v>
+        <v>-2.2233</v>
       </c>
       <c r="Q20" t="n">
-        <v>-12.5994</v>
+        <v>-3.891</v>
       </c>
       <c r="R20" t="n">
-        <v>20.7519</v>
+        <v>1.6676</v>
       </c>
       <c r="S20" t="n">
-        <v>11.1505</v>
+        <v>0.05349999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>10.5033</v>
+        <v>-0.2102</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6475999999999998</v>
+        <v>0.2637</v>
       </c>
       <c r="V20" t="n">
-        <v>-10.3844</v>
+        <v>-3.4622</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.9484</v>
+        <v>-1.26</v>
       </c>
       <c r="X20" t="n">
-        <v>-9.436199999999999</v>
+        <v>-2.2022</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. VIGARIO CONSTANTINO</t>
+          <t>A. GALLEGO CONTRERAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2044,70 +2044,70 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.0989</v>
+        <v>-9.4453</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.188800000000001</v>
+        <v>-8.1706</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9101</v>
+        <v>-1.2751</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6682</v>
+        <v>-15.0776</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1856</v>
+        <v>-14.455</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8541000000000001</v>
+        <v>-0.6222999999999994</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3813999999999999</v>
+        <v>-1.971900000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>1.4942</v>
+        <v>-5.188099999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.8757</v>
+        <v>3.2157</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2871</v>
+        <v>-13.1056</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3086</v>
+        <v>-9.266999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>1.0214</v>
+        <v>-3.8385</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.2233</v>
+        <v>8.1524</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.891</v>
+        <v>-12.5994</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6676</v>
+        <v>20.7519</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7452000000000001</v>
+        <v>7.863899999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6565</v>
+        <v>7.3492</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.08860000000000001</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>-3.4622</v>
+        <v>-10.3844</v>
       </c>
       <c r="W21" t="n">
-        <v>-1.26</v>
+        <v>-0.9484</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.2022</v>
+        <v>-9.436199999999999</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>25</v>
       </c>
       <c r="D22" t="n">
-        <v>-24.2873</v>
+        <v>-14.169</v>
       </c>
       <c r="E22" t="n">
-        <v>-27.22</v>
+        <v>-17.7155</v>
       </c>
       <c r="F22" t="n">
-        <v>2.9328</v>
+        <v>3.5469</v>
       </c>
       <c r="G22" t="n">
         <v>-28.1364</v>
@@ -2170,13 +2170,13 @@
         <v>42.8014</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.3973</v>
+        <v>7.7215</v>
       </c>
       <c r="T22" t="n">
-        <v>-4.4776</v>
+        <v>5.0272</v>
       </c>
       <c r="U22" t="n">
-        <v>2.08</v>
+        <v>2.6943</v>
       </c>
       <c r="V22" t="n">
         <v>10.508</v>
@@ -2203,22 +2203,22 @@
         <v>26</v>
       </c>
       <c r="D23" t="n">
-        <v>187.1978999999999</v>
+        <v>212.2108</v>
       </c>
       <c r="E23" t="n">
-        <v>149.3435</v>
+        <v>156.7291</v>
       </c>
       <c r="F23" t="n">
-        <v>37.8539</v>
+        <v>55.4822</v>
       </c>
       <c r="G23" t="n">
-        <v>82.57860000000001</v>
+        <v>82.57860000000002</v>
       </c>
       <c r="H23" t="n">
-        <v>1.362299999999992</v>
+        <v>1.362300000000005</v>
       </c>
       <c r="I23" t="n">
-        <v>81.21440000000001</v>
+        <v>81.21440000000003</v>
       </c>
       <c r="J23" t="n">
         <v>267.4857</v>
@@ -2239,7 +2239,7 @@
         <v>-49.46039999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>3.705500000000001</v>
+        <v>3.705499999999996</v>
       </c>
       <c r="Q23" t="n">
         <v>-394.66</v>
@@ -2248,16 +2248,16 @@
         <v>398.3674999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>76.68320000000001</v>
+        <v>101.6969</v>
       </c>
       <c r="T23" t="n">
-        <v>81.77970000000001</v>
+        <v>89.16679999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-5.097700000000001</v>
+        <v>12.5309</v>
       </c>
       <c r="V23" t="n">
-        <v>24.23060000000001</v>
+        <v>24.2306</v>
       </c>
       <c r="W23" t="n">
         <v>194.7394</v>
